--- a/Proyecto/entrenamiento/figures/metrics_comparison/Evaluacion_Inicial.xlsx
+++ b/Proyecto/entrenamiento/figures/metrics_comparison/Evaluacion_Inicial.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danil\OneDrive\Escritorio\Universidad\Cuarto\TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5577A15-0AA7-4A8A-9D49-30FEEF2E1F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA31561-5B4E-4211-A8E7-426329A9010B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{20EDC588-A743-43B1-973B-9032180DE140}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{20EDC588-A743-43B1-973B-9032180DE140}"/>
   </bookViews>
   <sheets>
     <sheet name="ShiftedMAPE" sheetId="1" r:id="rId1"/>
     <sheet name="NotShiftedMAPE" sheetId="3" r:id="rId2"/>
+    <sheet name="Red_Neuronal_Sin_Ajuste" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="16">
   <si>
     <t>Modelos</t>
   </si>
@@ -79,6 +80,12 @@
   </si>
   <si>
     <t>Salidas Únicas</t>
+  </si>
+  <si>
+    <t>Modelo</t>
+  </si>
+  <si>
+    <t>Red Neuronal (sin ajuste de pesos)</t>
   </si>
 </sst>
 </file>
@@ -195,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -215,10 +222,13 @@
     <xf numFmtId="11" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -570,13 +580,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7320F3A-78C5-4215-99E1-88E9BEC9115C}">
   <dimension ref="A1:J18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.6328125" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
     <col min="2" max="15" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>7</v>
       </c>
@@ -590,7 +600,7 @@
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
     </row>
-    <row r="2" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="8" t="s">
         <v>4</v>
@@ -608,7 +618,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
     </row>
-    <row r="3" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -640,7 +650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -672,7 +682,7 @@
         <v>0.54455500000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -704,7 +714,7 @@
         <v>0.88461900000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -736,7 +746,7 @@
         <v>0.88299899999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -768,7 +778,7 @@
         <v>0.86690299999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
@@ -800,32 +810,32 @@
         <v>0.83809299999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="9" t="s">
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12"/>
+    </row>
+    <row r="12" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7" t="s">
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+    </row>
+    <row r="13" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -848,7 +858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
@@ -859,7 +869,7 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
@@ -870,7 +880,7 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -893,7 +903,7 @@
         <v>0.88299899999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
@@ -916,7 +926,7 @@
         <v>0.86690299999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1052,13 +1062,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94DB0EE0-3D6B-4C12-BC5A-D6AA6CFFEABD}">
   <dimension ref="A1:J18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.6328125" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
     <col min="2" max="10" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="42.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="42.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>7</v>
       </c>
@@ -1072,7 +1082,7 @@
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
     </row>
-    <row r="2" spans="1:10" ht="42.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="42.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="8" t="s">
         <v>4</v>
@@ -1090,7 +1100,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
     </row>
-    <row r="3" spans="1:10" ht="42.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="42.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1122,7 +1132,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="42.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="42.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -1154,7 +1164,7 @@
         <v>0.54455529999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="42.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="42.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -1186,7 +1196,7 @@
         <v>0.88461909999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="42.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="42.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -1218,7 +1228,7 @@
         <v>0.88299899999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="42.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="42.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -1250,7 +1260,7 @@
         <v>0.86690310000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="42.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="42.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
@@ -1282,32 +1292,32 @@
         <v>0.83809350000000005</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="1:10" ht="28.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="9" t="s">
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:10" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" spans="1:10" ht="28.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12"/>
+    </row>
+    <row r="12" spans="1:10" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7" t="s">
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="28.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+    </row>
+    <row r="13" spans="1:10" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -1330,7 +1340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="28.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,7 +1351,7 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="28.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
@@ -1352,7 +1362,7 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="28.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -1375,7 +1385,7 @@
         <v>0.88299899999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="28.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1398,7 +1408,7 @@
         <v>0.86690310000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="28.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1529,4 +1539,105 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F50FBF3E-A7FC-48D9-9CAB-7D60014B3F0D}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="2" max="10" width="14.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4"/>
+      <c r="B1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="61.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1.745E-2</v>
+      </c>
+      <c r="C3" s="5">
+        <v>8.0914000000000003E-3</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0.59245000000000003</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.1729</v>
+      </c>
+      <c r="F3" s="5">
+        <v>8.5478999999999999E-2</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.54185000000000005</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1.4760000000000001E-2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>5710671.5</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0.78122999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>